--- a/ComponentList_V1.0.xlsx
+++ b/ComponentList_V1.0.xlsx
@@ -476,12 +476,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="1" min="1" max="1"/>
     <col width="47.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="8.88671875" customWidth="1" style="1" min="3" max="3"/>
+    <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,9 +506,14 @@
           <t>Satuan</t>
         </is>
       </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -515,7 +521,7 @@
           <t>Arduino Uno</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -523,9 +529,14 @@
           <t>Unit</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1 board per kelompok (3 orang)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -533,7 +544,7 @@
           <t>Breadboard full-size</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -541,94 +552,147 @@
           <t>Unit</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Per kelompok</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Potensiometer 3-pin 1k-20k (breadboard)</t>
+        </is>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>A0 = Vpack, A1 = Ipack, A2 = suhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>LED 5mm - Merah</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C5" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>LED status - 1 dipakai + 1 cadangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>LED 5mm - Kuning</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>LED status - 1 dipakai + 1 cadangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>LED 5mm - Hijau</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>LED status - 1 dipakai + 1 cadangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Resistor 330 1/4W Through-hole</t>
+        </is>
+      </c>
+      <c r="C8" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Resistor 330 1/4W Through-hole</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1 per LED (D8-D10) - 3 dipakai + 3 cadangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Kabel Dupont Breadboard Jumper Male-to-Male 40p 30cm</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Set</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Per kelompok</t>
         </is>
       </c>
     </row>
